--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4392,23 +4392,59 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="3" t="n"/>
-      <c r="C65" s="3" t="n"/>
-      <c r="D65" s="3" t="n"/>
-      <c r="E65" s="3" t="n"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>16291.76</v>
+      </c>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
-      <c r="J65" s="3" t="n"/>
-      <c r="K65" s="3" t="n"/>
-      <c r="L65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="N65" s="3" t="n"/>
-      <c r="O65" s="3" t="n"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>PCB、医药/消费、建材/玻璃</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="n"/>
-      <c r="Q65" s="3" t="n"/>
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16291.76亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4447,23 +4447,59 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n"/>
-      <c r="B66" s="3" t="n"/>
-      <c r="C66" s="3" t="n"/>
-      <c r="D66" s="3" t="n"/>
-      <c r="E66" s="3" t="n"/>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>16127.17</v>
+      </c>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="n"/>
-      <c r="L66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="N66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="3" t="n"/>
-      <c r="Q66" s="3" t="n"/>
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16127.17亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4502,23 +4502,59 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n"/>
-      <c r="B67" s="3" t="n"/>
-      <c r="C67" s="3" t="n"/>
-      <c r="D67" s="3" t="n"/>
-      <c r="E67" s="3" t="n"/>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>18391.22</v>
+      </c>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
-      <c r="J67" s="3" t="n"/>
-      <c r="K67" s="3" t="n"/>
-      <c r="L67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="N67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>汽车零部件、其他涨停</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr"/>
       <c r="P67" s="3" t="n"/>
-      <c r="Q67" s="3" t="n"/>
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约18391.22亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：汽车零部件。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4557,23 +4557,59 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="3" t="n"/>
-      <c r="C68" s="3" t="n"/>
-      <c r="D68" s="3" t="n"/>
-      <c r="E68" s="3" t="n"/>
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>18231.34</v>
+      </c>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr"/>
       <c r="P68" s="3" t="n"/>
-      <c r="Q68" s="3" t="n"/>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约18231.34亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4612,23 +4612,59 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n"/>
-      <c r="B69" s="3" t="n"/>
-      <c r="C69" s="3" t="n"/>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="3" t="n"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>20771</v>
+      </c>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="3" t="n"/>
-      <c r="L69" s="3" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="N69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="n"/>
-      <c r="Q69" s="3" t="n"/>
+      <c r="Q69" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约20771.0亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4667,23 +4667,59 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n"/>
-      <c r="B70" s="3" t="n"/>
-      <c r="C70" s="3" t="n"/>
-      <c r="D70" s="3" t="n"/>
-      <c r="E70" s="3" t="n"/>
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>20315.13</v>
+      </c>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
-      <c r="J70" s="3" t="n"/>
-      <c r="K70" s="3" t="n"/>
-      <c r="L70" s="3" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="N70" s="3" t="n"/>
-      <c r="O70" s="3" t="n"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr"/>
       <c r="P70" s="3" t="n"/>
-      <c r="Q70" s="3" t="n"/>
+      <c r="Q70" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约20315.13亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4722,23 +4722,59 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="3" t="n"/>
-      <c r="C71" s="3" t="n"/>
-      <c r="D71" s="3" t="n"/>
-      <c r="E71" s="3" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>21355.5</v>
+      </c>
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="n"/>
-      <c r="L71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
-      <c r="N71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="n"/>
-      <c r="Q71" s="3" t="n"/>
+      <c r="Q71" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约21355.5亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4777,23 +4777,59 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n"/>
-      <c r="B72" s="3" t="n"/>
-      <c r="C72" s="3" t="n"/>
-      <c r="D72" s="3" t="n"/>
-      <c r="E72" s="3" t="n"/>
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>17649.76</v>
+      </c>
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="3" t="n"/>
-      <c r="Q72" s="3" t="n"/>
+      <c r="Q72" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约17649.76亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4832,23 +4832,59 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="3" t="n"/>
-      <c r="C73" s="3" t="n"/>
-      <c r="D73" s="3" t="n"/>
-      <c r="E73" s="3" t="n"/>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>16533.57</v>
+      </c>
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="n"/>
-      <c r="Q73" s="3" t="n"/>
+      <c r="Q73" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16533.57亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4887,23 +4887,59 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n"/>
-      <c r="B74" s="3" t="n"/>
-      <c r="C74" s="3" t="n"/>
-      <c r="D74" s="3" t="n"/>
-      <c r="E74" s="3" t="n"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>-0.0234</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>-0.0268</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>16533.57</v>
+      </c>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="n"/>
-      <c r="H74" s="3" t="n"/>
-      <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="n"/>
-      <c r="L74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="N74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr"/>
       <c r="P74" s="3" t="n"/>
-      <c r="Q74" s="3" t="n"/>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16533.57亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4942,23 +4942,59 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n"/>
-      <c r="B75" s="3" t="n"/>
-      <c r="C75" s="3" t="n"/>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="3" t="n"/>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>-0.0344</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>17027.99</v>
+      </c>
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n"/>
-      <c r="H75" s="3" t="n"/>
-      <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="n"/>
-      <c r="L75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="N75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr"/>
       <c r="P75" s="3" t="n"/>
-      <c r="Q75" s="3" t="n"/>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约17027.99亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4997,23 +4997,59 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n"/>
-      <c r="B76" s="3" t="n"/>
-      <c r="C76" s="3" t="n"/>
-      <c r="D76" s="3" t="n"/>
-      <c r="E76" s="3" t="n"/>
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>14091.98</v>
+      </c>
       <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="3" t="n"/>
-      <c r="L76" s="3" t="n"/>
-      <c r="M76" s="3" t="n"/>
-      <c r="N76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr"/>
       <c r="P76" s="3" t="n"/>
-      <c r="Q76" s="3" t="n"/>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14091.98亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5052,23 +5052,59 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n"/>
-      <c r="B77" s="3" t="n"/>
-      <c r="C77" s="3" t="n"/>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="3" t="n"/>
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>14380.18</v>
+      </c>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="n"/>
-      <c r="L77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="n"/>
-      <c r="Q77" s="3" t="n"/>
+      <c r="Q77" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14380.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5107,23 +5107,59 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n"/>
-      <c r="B78" s="3" t="n"/>
-      <c r="C78" s="3" t="n"/>
-      <c r="D78" s="3" t="n"/>
-      <c r="E78" s="3" t="n"/>
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>14380.18</v>
+      </c>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>
-      <c r="H78" s="3" t="n"/>
-      <c r="I78" s="3" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="n"/>
-      <c r="L78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="N78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="inlineStr"/>
       <c r="P78" s="3" t="n"/>
-      <c r="Q78" s="3" t="n"/>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14380.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5162,23 +5162,59 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n"/>
-      <c r="B79" s="3" t="n"/>
-      <c r="C79" s="3" t="n"/>
-      <c r="D79" s="3" t="n"/>
-      <c r="E79" s="3" t="n"/>
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>14380.18</v>
+      </c>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="3" t="n"/>
-      <c r="H79" s="3" t="n"/>
-      <c r="I79" s="3" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="n"/>
-      <c r="L79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
-      <c r="N79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="3" t="n"/>
-      <c r="Q79" s="3" t="n"/>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14380.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5217,23 +5217,59 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n"/>
-      <c r="B80" s="3" t="n"/>
-      <c r="C80" s="3" t="n"/>
-      <c r="D80" s="3" t="n"/>
-      <c r="E80" s="3" t="n"/>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>14380.18</v>
+      </c>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="3" t="n"/>
-      <c r="H80" s="3" t="n"/>
-      <c r="I80" s="3" t="n"/>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="n"/>
-      <c r="L80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="N80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="inlineStr"/>
       <c r="P80" s="3" t="n"/>
-      <c r="Q80" s="3" t="n"/>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14380.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5272,23 +5272,59 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n"/>
-      <c r="B81" s="3" t="n"/>
-      <c r="C81" s="3" t="n"/>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>14380.18</v>
+      </c>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="n"/>
-      <c r="L81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
-      <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="3" t="n"/>
-      <c r="Q81" s="3" t="n"/>
+      <c r="Q81" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14380.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5327,23 +5327,59 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n"/>
-      <c r="B82" s="3" t="n"/>
-      <c r="C82" s="3" t="n"/>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>16821.27</v>
+      </c>
       <c r="F82" s="3" t="n"/>
       <c r="G82" s="3" t="n"/>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="3" t="n"/>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="3" t="n"/>
-      <c r="L82" s="3" t="n"/>
-      <c r="M82" s="3" t="n"/>
-      <c r="N82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="inlineStr"/>
       <c r="P82" s="3" t="n"/>
-      <c r="Q82" s="3" t="n"/>
+      <c r="Q82" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16821.27亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5382,23 +5382,59 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n"/>
-      <c r="B83" s="3" t="n"/>
-      <c r="C83" s="3" t="n"/>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>19005.55</v>
+      </c>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="n"/>
-      <c r="L83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr"/>
       <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="n"/>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约19005.55亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5437,23 +5437,59 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n"/>
-      <c r="B84" s="3" t="n"/>
-      <c r="C84" s="3" t="n"/>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>-0.0261</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>15378.31</v>
+      </c>
       <c r="F84" s="3" t="n"/>
       <c r="G84" s="3" t="n"/>
-      <c r="H84" s="3" t="n"/>
-      <c r="I84" s="3" t="n"/>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="3" t="n"/>
-      <c r="L84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="N84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="inlineStr"/>
       <c r="P84" s="3" t="n"/>
-      <c r="Q84" s="3" t="n"/>
+      <c r="Q84" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约15378.31亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5492,23 +5492,59 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n"/>
-      <c r="B85" s="3" t="n"/>
-      <c r="C85" s="3" t="n"/>
-      <c r="D85" s="3" t="n"/>
-      <c r="E85" s="3" t="n"/>
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>16759.18</v>
+      </c>
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
-      <c r="I85" s="3" t="n"/>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="n"/>
-      <c r="L85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
-      <c r="N85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>PCB、其他涨停</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="3" t="n"/>
-      <c r="Q85" s="3" t="n"/>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约16759.18亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：PCB。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5547,23 +5547,59 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n"/>
-      <c r="B86" s="3" t="n"/>
-      <c r="C86" s="3" t="n"/>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="3" t="n"/>
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>-0.0197</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>14144.02</v>
+      </c>
       <c r="F86" s="3" t="n"/>
       <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="n"/>
-      <c r="L86" s="3" t="n"/>
-      <c r="M86" s="3" t="n"/>
-      <c r="N86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="3" t="n"/>
-      <c r="Q86" s="3" t="n"/>
+      <c r="Q86" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约14144.02亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5602,23 +5602,59 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n"/>
-      <c r="B87" s="3" t="n"/>
-      <c r="C87" s="3" t="n"/>
-      <c r="D87" s="3" t="n"/>
-      <c r="E87" s="3" t="n"/>
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>16330.05</v>
+      </c>
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="n"/>
-      <c r="L87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
-      <c r="N87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="inlineStr"/>
       <c r="P87" s="3" t="n"/>
-      <c r="Q87" s="3" t="n"/>
+      <c r="Q87" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16330.05亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5657,23 +5657,59 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n"/>
-      <c r="B88" s="3" t="n"/>
-      <c r="C88" s="3" t="n"/>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="3" t="n"/>
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>15554.21</v>
+      </c>
       <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="N88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="inlineStr"/>
       <c r="P88" s="3" t="n"/>
-      <c r="Q88" s="3" t="n"/>
+      <c r="Q88" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约15554.21亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5712,23 +5712,59 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n"/>
-      <c r="B89" s="3" t="n"/>
-      <c r="C89" s="3" t="n"/>
-      <c r="D89" s="3" t="n"/>
-      <c r="E89" s="3" t="n"/>
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>14375.12</v>
+      </c>
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="n"/>
-      <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
-      <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="inlineStr"/>
       <c r="P89" s="3" t="n"/>
-      <c r="Q89" s="3" t="n"/>
+      <c r="Q89" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14375.12亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5767,23 +5767,59 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n"/>
-      <c r="B90" s="3" t="n"/>
-      <c r="C90" s="3" t="n"/>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="3" t="n"/>
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>14561.12</v>
+      </c>
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
-      <c r="H90" s="3" t="n"/>
-      <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="n"/>
-      <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="N90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>震荡</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>2-4成</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="inlineStr"/>
       <c r="P90" s="3" t="n"/>
-      <c r="Q90" s="3" t="n"/>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡，指数分化但创业板较强，两市成交额约14561.12亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5822,23 +5822,59 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n"/>
-      <c r="B91" s="3" t="n"/>
-      <c r="C91" s="3" t="n"/>
-      <c r="D91" s="3" t="n"/>
-      <c r="E91" s="3" t="n"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>14293.48</v>
+      </c>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
-      <c r="H91" s="3" t="n"/>
-      <c r="I91" s="3" t="n"/>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="n"/>
-      <c r="L91" s="3" t="n"/>
-      <c r="M91" s="3" t="n"/>
-      <c r="N91" s="3" t="n"/>
-      <c r="O91" s="3" t="n"/>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="3" t="n"/>
-      <c r="Q91" s="3" t="n"/>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约14293.48亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5877,23 +5877,59 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n"/>
-      <c r="B92" s="3" t="n"/>
-      <c r="C92" s="3" t="n"/>
-      <c r="D92" s="3" t="n"/>
-      <c r="E92" s="3" t="n"/>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>-0.0296</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>15287.14</v>
+      </c>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="n"/>
-      <c r="L92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
-      <c r="N92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="inlineStr"/>
       <c r="P92" s="3" t="n"/>
-      <c r="Q92" s="3" t="n"/>
+      <c r="Q92" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约15287.14亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5932,23 +5932,59 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n"/>
-      <c r="B93" s="3" t="n"/>
-      <c r="C93" s="3" t="n"/>
-      <c r="D93" s="3" t="n"/>
-      <c r="E93" s="3" t="n"/>
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0.0279</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>19562.84</v>
+      </c>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="N93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="n"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约19562.84亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5987,23 +5987,59 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n"/>
-      <c r="B94" s="3" t="n"/>
-      <c r="C94" s="3" t="n"/>
-      <c r="D94" s="3" t="n"/>
-      <c r="E94" s="3" t="n"/>
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>-0.0119</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>16087.93</v>
+      </c>
       <c r="F94" s="3" t="n"/>
       <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="n"/>
-      <c r="L94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
-      <c r="N94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="3" t="n"/>
-      <c r="Q94" s="3" t="n"/>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16087.93亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6042,23 +6042,59 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n"/>
-      <c r="B95" s="3" t="n"/>
-      <c r="C95" s="3" t="n"/>
-      <c r="D95" s="3" t="n"/>
-      <c r="E95" s="3" t="n"/>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>-0.0341</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>14609.58</v>
+      </c>
       <c r="F95" s="3" t="n"/>
       <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="n"/>
-      <c r="L95" s="3" t="n"/>
-      <c r="M95" s="3" t="n"/>
-      <c r="N95" s="3" t="n"/>
-      <c r="O95" s="3" t="n"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="inlineStr"/>
       <c r="P95" s="3" t="n"/>
-      <c r="Q95" s="3" t="n"/>
+      <c r="Q95" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约14609.58亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,8 +851,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6097,23 +6097,59 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n"/>
-      <c r="B96" s="3" t="n"/>
-      <c r="C96" s="3" t="n"/>
-      <c r="D96" s="3" t="n"/>
-      <c r="E96" s="3" t="n"/>
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.0202</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>16284.88</v>
+      </c>
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="n"/>
-      <c r="L96" s="3" t="n"/>
-      <c r="M96" s="3" t="n"/>
-      <c r="N96" s="3" t="n"/>
-      <c r="O96" s="3" t="n"/>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏强</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>3-5成</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="inlineStr"/>
       <c r="P96" s="3" t="n"/>
-      <c r="Q96" s="3" t="n"/>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏强，指数分化但创业板较强，两市成交额约16284.88亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6152,23 +6152,59 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n"/>
-      <c r="B97" s="3" t="n"/>
-      <c r="C97" s="3" t="n"/>
-      <c r="D97" s="3" t="n"/>
-      <c r="E97" s="3" t="n"/>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>15565.24</v>
+      </c>
       <c r="F97" s="3" t="n"/>
       <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="n"/>
-      <c r="L97" s="3" t="n"/>
-      <c r="M97" s="3" t="n"/>
-      <c r="N97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="n"/>
-      <c r="Q97" s="3" t="n"/>
+      <c r="Q97" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约15565.24亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>

--- a/每日A股复盘表.xlsx
+++ b/每日A股复盘表.xlsx
@@ -851,9 +851,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A3:J3"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6207,23 +6207,59 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n"/>
-      <c r="B98" s="3" t="n"/>
-      <c r="C98" s="3" t="n"/>
-      <c r="D98" s="3" t="n"/>
-      <c r="E98" s="3" t="n"/>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>-0.0273</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>16744.68</v>
+      </c>
       <c r="F98" s="3" t="n"/>
       <c r="G98" s="3" t="n"/>
-      <c r="H98" s="3" t="n"/>
-      <c r="I98" s="3" t="n"/>
-      <c r="J98" s="3" t="n"/>
-      <c r="K98" s="3" t="n"/>
-      <c r="L98" s="3" t="n"/>
-      <c r="M98" s="3" t="n"/>
-      <c r="N98" s="3" t="n"/>
-      <c r="O98" s="3" t="n"/>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>震荡偏弱</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>1-2成</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
+          <t>其他涨停</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="inlineStr"/>
       <c r="P98" s="3" t="n"/>
-      <c r="Q98" s="3" t="n"/>
+      <c r="Q98" s="3" t="inlineStr">
+        <is>
+          <t>市场震荡偏弱，指数分化但创业板较强，两市成交额约16744.68亿元，个股宽度使用排行样本估算，强势样本中涨停/20cm个股活跃。当前强势方向：其他涨停。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
